--- a/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_simplified_flop_strategy.xlsx
+++ b/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_simplified_flop_strategy.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R63589ae7f2b74777"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="Rb55390f641ae4a46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="Rf6f7e5ba92254a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="Rb44d7c62bf624cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="R49b36ee5fa6940a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="Rd6cbc74a099d42ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2e9bee9f610e4e5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="R429e677f89764155"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="R3782d56258e240c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R5c1f34353b5547c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="Rcda33f4aacd64f85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="Redb848b8a7ac414b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1421,19 +1421,19 @@
         <x:v>Two pair+</x:v>
       </x:c>
       <x:c r="B7" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="C7" s="62" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="D7" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="E7" s="62" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="F7" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="G7" s="62" t="str">
         <x:v>B</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="K7" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="L7" s="64" t="str">
         <x:v>X</x:v>
@@ -1483,16 +1483,16 @@
         <x:v>—</x:v>
       </x:c>
       <x:c r="H8" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="I8" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="J8" s="45" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="K8" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="L8" s="64" t="str">
         <x:v>X</x:v>
@@ -1662,7 +1662,7 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="I12" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="J12" s="41" t="str">
         <x:v>X/B</x:v>
@@ -1700,7 +1700,7 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="G13" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="H13" s="55" t="str">
         <x:v>X</x:v>
@@ -1729,7 +1729,7 @@
         <x:v>OESD</x:v>
       </x:c>
       <x:c r="B14" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="C14" s="64" t="str">
         <x:v>X</x:v>
@@ -1747,16 +1747,16 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="H14" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="I14" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="J14" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="K14" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="L14" s="64" t="str">
         <x:v>X</x:v>
@@ -1776,13 +1776,13 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="C15" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="D15" s="56" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="E15" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="F15" s="58" t="str">
         <x:v>B</x:v>
@@ -1794,13 +1794,13 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="I15" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="J15" s="58" t="str">
         <x:v>B</x:v>
       </x:c>
       <x:c r="K15" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="L15" s="65" t="str">
         <x:v>X</x:v>
@@ -2088,7 +2088,7 @@
         <x:v>Two pair+</x:v>
       </x:c>
       <x:c r="B7" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="C7" s="62" t="str">
         <x:v>B</x:v>
@@ -2106,7 +2106,7 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="H7" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="I7" s="62" t="str">
         <x:v>B</x:v>
@@ -2220,7 +2220,7 @@
         <x:v>Underpair</x:v>
       </x:c>
       <x:c r="B10" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="C10" s="63" t="str">
         <x:v>—</x:v>
@@ -2253,10 +2253,10 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="M10" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="N10" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -2276,7 +2276,7 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="F11" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="G11" s="62" t="str">
         <x:v>B</x:v>
@@ -2288,16 +2288,16 @@
         <x:v>X</x:v>
       </x:c>
       <x:c r="J11" s="41" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="K11" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="L11" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="M11" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="N11" s="62" t="str">
         <x:v>B</x:v>
@@ -2338,10 +2338,10 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="L12" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="M12" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="N12" s="62" t="str">
         <x:v>B</x:v>
@@ -2367,7 +2367,7 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="G13" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="H13" s="55" t="str">
         <x:v>X</x:v>
@@ -2385,10 +2385,10 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="M13" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="N13" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
@@ -2440,7 +2440,7 @@
         <x:v>Gutshot</x:v>
       </x:c>
       <x:c r="B15" s="56" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="C15" s="68" t="str">
         <x:v>B</x:v>
@@ -2461,7 +2461,7 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="I15" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="J15" s="58" t="str">
         <x:v>B</x:v>
@@ -2517,10 +2517,10 @@
         <x:v>B</x:v>
       </x:c>
       <x:c r="M16" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="N16" s="66" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
@@ -2564,7 +2564,7 @@
         <x:v>X/B</x:v>
       </x:c>
       <x:c r="N17" s="69" t="str">
-        <x:v>X/B</x:v>
+        <x:v>B/X</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2764,7 +2764,7 @@
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="E7" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="F7" s="49" t="str">
         <x:v>C</x:v>
@@ -2776,7 +2776,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="I7" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="J7" s="41" t="str">
         <x:v>C/R</x:v>
@@ -2785,10 +2785,10 @@
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="L7" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="M7" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="N7" s="85" t="str">
         <x:v>R</x:v>
@@ -2978,13 +2978,13 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="C12" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="D12" s="49" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="E12" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="F12" s="49" t="str">
         <x:v>C</x:v>
@@ -3034,7 +3034,7 @@
         <x:v>F</x:v>
       </x:c>
       <x:c r="G13" s="66" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
       <x:c r="H13" s="80" t="str">
         <x:v>F</x:v>
@@ -3049,7 +3049,7 @@
         <x:v>F/C</x:v>
       </x:c>
       <x:c r="L13" s="66" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
       <x:c r="M13" s="66" t="str">
         <x:v>F/C</x:v>
@@ -3069,7 +3069,7 @@
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="D14" s="41" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="E14" s="63" t="str">
         <x:v>—</x:v>
@@ -3084,22 +3084,22 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="I14" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="J14" s="41" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="K14" s="69" t="str">
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="L14" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="M14" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="N14" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
@@ -3131,19 +3131,19 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="J15" s="56" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="K15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="L15" s="84" t="str">
         <x:v>R</x:v>
       </x:c>
       <x:c r="M15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="N15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
@@ -3187,7 +3187,7 @@
         <x:v>C/R</x:v>
       </x:c>
       <x:c r="N16" s="66" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
@@ -3437,13 +3437,13 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="G7" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="H7" s="49" t="str">
         <x:v>C</x:v>
       </x:c>
       <x:c r="I7" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="J7" s="75" t="str">
         <x:v>R</x:v>
@@ -3490,10 +3490,10 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="J8" s="41" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="K8" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="L8" s="64" t="str">
         <x:v>C</x:v>
@@ -3546,7 +3546,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="N9" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
@@ -3604,7 +3604,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="D11" s="41" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
       <x:c r="E11" s="64" t="str">
         <x:v>C</x:v>
@@ -3622,10 +3622,10 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="J11" s="41" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="K11" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="L11" s="64" t="str">
         <x:v>C</x:v>
@@ -3748,7 +3748,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="H14" s="41" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
       <x:c r="I14" s="64" t="str">
         <x:v>C</x:v>
@@ -3798,19 +3798,19 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="J15" s="56" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="K15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="L15" s="84" t="str">
         <x:v>R</x:v>
       </x:c>
       <x:c r="M15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
       <x:c r="N15" s="66" t="str">
-        <x:v>C/R</x:v>
+        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
@@ -3851,7 +3851,7 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="M16" s="66" t="str">
-        <x:v>F/C</x:v>
+        <x:v>C/F</x:v>
       </x:c>
       <x:c r="N16" s="66" t="str">
         <x:v>F/C</x:v>
@@ -3995,7 +3995,7 @@
         <x:v>Микс</x:v>
       </x:c>
       <x:c r="B9" s="87" t="str">
-        <x:v>Иначе два наиболее частых действия, строго 50/50</x:v>
+        <x:v>Иначе два наиболее частых действия, строго 50/50; первым указано более частое действие солвера</x:v>
       </x:c>
       <x:c r="C9" s="3"/>
       <x:c r="D9" s="3"/>

--- a/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_simplified_flop_strategy.xlsx
+++ b/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_simplified_flop_strategy.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2e9bee9f610e4e5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="R429e677f89764155"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="R3782d56258e240c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R5c1f34353b5547c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="Rcda33f4aacd64f85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="Redb848b8a7ac414b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd9c6ab5b75a54ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="R3ecb4b5b6bb9470c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="Rba2303a3c7754707"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R097ad820e8be473c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="Ra6d00eb73eb34121"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="R822310e1cd6241da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -546,10 +546,10 @@
     <x:xf numFmtId="0" fontId="11" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="10" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -821,7 +821,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="str">
-        <x:v>11 категорий рук × 13 узких категорий флопов B13. Чистое действие или строгий микс 50/50.</x:v>
+        <x:v>12 категорий рук × 13 узких категорий флопов B13. Чистое действие или строгий микс 50/50.</x:v>
       </x:c>
       <x:c r="B3" s="7"/>
       <x:c r="C3" s="7"/>
@@ -891,13 +891,13 @@
         <x:v>X 78.2%; B 21.8%</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
-        <x:v>X 91.0%; B 9.0%</x:v>
+        <x:v>X 90.8%; B 9.2%</x:v>
       </x:c>
       <x:c r="F6" s="17" t="n">
-        <x:v>0.0014872884820423117</x:v>
+        <x:v>0.0016823883499330796</x:v>
       </x:c>
       <x:c r="G6" s="17" t="n">
-        <x:v>0.0014872884820423243</x:v>
+        <x:v>0.001682388349933094</x:v>
       </x:c>
       <x:c r="H6" s="17" t="n">
         <x:v>0</x:v>
@@ -906,7 +906,7 @@
         <x:v>80553</x:v>
       </x:c>
       <x:c r="J6" s="18" t="n">
-        <x:v>128</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -923,13 +923,13 @@
         <x:v>X 51.1%; B 48.9%</x:v>
       </x:c>
       <x:c r="E7" s="15" t="str">
-        <x:v>X 50.3%; B 49.7%</x:v>
+        <x:v>X 49.8%; B 50.2%</x:v>
       </x:c>
       <x:c r="F7" s="17" t="n">
-        <x:v>0.0020771704253783113</x:v>
+        <x:v>0.0020848457653751683</x:v>
       </x:c>
       <x:c r="G7" s="17" t="n">
-        <x:v>0.0016241274976155563</x:v>
+        <x:v>0.0016301288014037006</x:v>
       </x:c>
       <x:c r="H7" s="17" t="n">
         <x:v>0</x:v>
@@ -938,7 +938,7 @@
         <x:v>61270</x:v>
       </x:c>
       <x:c r="J7" s="18" t="n">
-        <x:v>122</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -955,13 +955,13 @@
         <x:v>F 34.8%; C 52.4%; R 12.7%</x:v>
       </x:c>
       <x:c r="E8" s="15" t="str">
-        <x:v>F 37.9%; C 54.7%; R 7.4%</x:v>
+        <x:v>F 34.7%; C 57.9%; R 7.4%</x:v>
       </x:c>
       <x:c r="F8" s="17" t="n">
-        <x:v>0.019168192826146336</x:v>
+        <x:v>0.016636724878319832</x:v>
       </x:c>
       <x:c r="G8" s="17" t="n">
-        <x:v>0.004180694168933864</x:v>
+        <x:v>0.0036285663087693354</x:v>
       </x:c>
       <x:c r="H8" s="17" t="n">
         <x:v>0</x:v>
@@ -970,7 +970,7 @@
         <x:v>61270</x:v>
       </x:c>
       <x:c r="J8" s="18" t="n">
-        <x:v>122</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -987,13 +987,13 @@
         <x:v>F 40.0%; C 48.1%; R 11.9%</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
-        <x:v>F 46.2%; C 46.1%; R 7.7%</x:v>
+        <x:v>F 44.7%; C 47.6%; R 7.7%</x:v>
       </x:c>
       <x:c r="F9" s="17" t="n">
-        <x:v>0.02103900936917471</x:v>
+        <x:v>0.016117697505484814</x:v>
       </x:c>
       <x:c r="G9" s="17" t="n">
-        <x:v>0.008036054845898514</x:v>
+        <x:v>0.006156311776420792</x:v>
       </x:c>
       <x:c r="H9" s="17" t="n">
         <x:v>0</x:v>
@@ -1002,7 +1002,7 @@
         <x:v>80002</x:v>
       </x:c>
       <x:c r="J9" s="18" t="n">
-        <x:v>128</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1116,7 +1116,7 @@
       <x:c r="D16" s="23"/>
       <x:c r="E16" s="3"/>
       <x:c r="F16" s="24" t="str">
-        <x:v>11 категорий рук: 7 made, OESD, Gutshot, 2 overcards + BDFD и Air.</x:v>
+        <x:v>12 категорий рук: 8 made, OESD, Gutshot, 2 overcards + BDFD и Air.</x:v>
       </x:c>
       <x:c r="G16" s="24"/>
       <x:c r="H16" s="24"/>
@@ -1681,222 +1681,266 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="54" t="str">
+      <x:c r="A13" s="37" t="str">
         <x:v>Weak pair</x:v>
       </x:c>
-      <x:c r="B13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="E13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="G13" s="66" t="str">
+      <x:c r="B13" s="41" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="C13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H13" s="41" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="I13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="K13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="M13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="54" t="str">
+        <x:v>Low pocket pair</x:v>
+      </x:c>
+      <x:c r="B14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C14" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E14" s="66" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="F14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G14" s="66" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="H14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I14" s="66" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="J14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="K14" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="L14" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="M14" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="N14" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="37" t="str">
+        <x:v>OESD</x:v>
+      </x:c>
+      <x:c r="B15" s="41" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="H13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="J13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="K13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="L13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="M13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="N13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="37" t="str">
-        <x:v>OESD</x:v>
-      </x:c>
-      <x:c r="B14" s="41" t="str">
+      <x:c r="C15" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D15" s="41" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="E15" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F15" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="G15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H15" s="41" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="C14" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D14" s="41" t="str">
-        <x:v>X/B</x:v>
-      </x:c>
-      <x:c r="E14" s="63" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F14" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="G14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="H14" s="41" t="str">
+      <x:c r="I15" s="69" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="I14" s="69" t="str">
+      <x:c r="J15" s="41" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="J14" s="41" t="str">
+      <x:c r="K15" s="69" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="K14" s="69" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="L14" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="M14" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="N14" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="54" t="str">
-        <x:v>Gutshot</x:v>
-      </x:c>
-      <x:c r="B15" s="58" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="C15" s="66" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="D15" s="56" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="E15" s="66" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="F15" s="58" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="G15" s="68" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="H15" s="56" t="str">
-        <x:v>X/B</x:v>
-      </x:c>
-      <x:c r="I15" s="66" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="J15" s="58" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="K15" s="66" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="L15" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="M15" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="N15" s="65" t="str">
+      <x:c r="L15" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="M15" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="N15" s="64" t="str">
         <x:v>X</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="54" t="str">
+        <x:v>Gutshot</x:v>
+      </x:c>
+      <x:c r="B16" s="58" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="C16" s="66" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="D16" s="56" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="E16" s="66" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="F16" s="58" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="G16" s="68" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H16" s="56" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="I16" s="66" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="J16" s="58" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="K16" s="66" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="L16" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="M16" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="N16" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="54" t="str">
         <x:v>2 overcards + BDFD</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="D16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="E16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="H16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="I16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="J16" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="K16" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="L16" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="M16" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="N16" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="37" t="str">
+      <x:c r="B17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="C17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="D17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="G17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="H17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J17" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="K17" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="L17" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="M17" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="N17" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="37" t="str">
         <x:v>Air</x:v>
       </x:c>
-      <x:c r="B17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="E17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="G17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="H17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="J17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="K17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="L17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="M17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="N17" s="64" t="str">
+      <x:c r="B18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="H18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="K18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="L18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="M18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="N18" s="64" t="str">
         <x:v>X</x:v>
       </x:c>
     </x:row>
@@ -2348,222 +2392,266 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="54" t="str">
+      <x:c r="A13" s="37" t="str">
         <x:v>Weak pair</x:v>
       </x:c>
-      <x:c r="B13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="E13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F13" s="56" t="str">
+      <x:c r="B13" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="G13" s="66" t="str">
+      <x:c r="C13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F13" s="41" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="G13" s="69" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="H13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="J13" s="55" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="K13" s="65" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="L13" s="66" t="str">
+      <x:c r="H13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I13" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="K13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L13" s="69" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="M13" s="66" t="str">
+      <x:c r="M13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N13" s="69" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="N13" s="66" t="str">
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="54" t="str">
+        <x:v>Low pocket pair</x:v>
+      </x:c>
+      <x:c r="B14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C14" s="66" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="D14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E14" s="66" t="str">
         <x:v>B/X</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="37" t="str">
+      <x:c r="F14" s="56" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="G14" s="66" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="H14" s="55" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I14" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J14" s="56" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="K14" s="65" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="L14" s="66" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="M14" s="66" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="N14" s="66" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="37" t="str">
         <x:v>OESD</x:v>
       </x:c>
-      <x:c r="B14" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="C14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D14" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E14" s="63" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F14" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="G14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="H14" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="I14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="J14" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="K14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="L14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="M14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="N14" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="54" t="str">
-        <x:v>Gutshot</x:v>
-      </x:c>
-      <x:c r="B15" s="56" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="C15" s="68" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D15" s="58" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E15" s="68" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="F15" s="58" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="G15" s="68" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="H15" s="56" t="str">
-        <x:v>X/B</x:v>
-      </x:c>
-      <x:c r="I15" s="66" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="J15" s="58" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="K15" s="68" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="L15" s="68" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="M15" s="68" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="N15" s="68" t="str">
+      <x:c r="B15" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="C15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D15" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E15" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F15" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="G15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H15" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="I15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="J15" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="K15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="L15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="M15" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="N15" s="62" t="str">
         <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="54" t="str">
+        <x:v>Gutshot</x:v>
+      </x:c>
+      <x:c r="B16" s="56" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="C16" s="68" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D16" s="58" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E16" s="68" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F16" s="58" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="G16" s="68" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H16" s="56" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="I16" s="66" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="J16" s="58" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="K16" s="68" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="L16" s="68" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="M16" s="68" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="N16" s="68" t="str">
+        <x:v>B</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="54" t="str">
         <x:v>2 overcards + BDFD</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="D16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="E16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="H16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="I16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="J16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="K16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="L16" s="68" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="M16" s="66" t="str">
+      <x:c r="B17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="C17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="D17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="G17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="H17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L17" s="68" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="M17" s="66" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="N16" s="66" t="str">
+      <x:c r="N17" s="66" t="str">
         <x:v>B/X</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="37" t="str">
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="37" t="str">
         <x:v>Air</x:v>
       </x:c>
-      <x:c r="B17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="C17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="E17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="G17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="H17" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I17" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="J17" s="41" t="str">
+      <x:c r="B18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="C18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="G18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="H18" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I18" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J18" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="K17" s="69" t="str">
+      <x:c r="K18" s="69" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="L17" s="69" t="str">
+      <x:c r="L18" s="69" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="M17" s="69" t="str">
+      <x:c r="M18" s="69" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="N17" s="69" t="str">
+      <x:c r="N18" s="69" t="str">
         <x:v>B/X</x:v>
       </x:c>
     </x:row>
@@ -3015,222 +3103,266 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="54" t="str">
+      <x:c r="A13" s="37" t="str">
         <x:v>Weak pair</x:v>
       </x:c>
-      <x:c r="B13" s="80" t="str">
-        <x:v>F</x:v>
+      <x:c r="B13" s="49" t="str">
+        <x:v>C</x:v>
       </x:c>
       <x:c r="C13" s="82" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="D13" s="80" t="str">
+      <x:c r="D13" s="79" t="str">
         <x:v>F</x:v>
       </x:c>
       <x:c r="E13" s="82" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="F13" s="80" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="G13" s="66" t="str">
+      <x:c r="F13" s="41" t="str">
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="G13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="H13" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="I13" s="69" t="str">
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="J13" s="41" t="str">
         <x:v>C/F</x:v>
       </x:c>
-      <x:c r="H13" s="80" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="I13" s="82" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="J13" s="56" t="str">
+      <x:c r="K13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L13" s="69" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+      <x:c r="M13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="54" t="str">
+        <x:v>Low pocket pair</x:v>
+      </x:c>
+      <x:c r="B14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="C14" s="83" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="E14" s="83" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="F14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G14" s="66" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+      <x:c r="H14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I14" s="83" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="J14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="K14" s="66" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="K13" s="66" t="str">
+      <x:c r="L14" s="66" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="L13" s="66" t="str">
-        <x:v>C/F</x:v>
-      </x:c>
-      <x:c r="M13" s="66" t="str">
+      <x:c r="M14" s="66" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="N13" s="65" t="str">
-        <x:v>C</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="37" t="str">
+      <x:c r="N14" s="66" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="37" t="str">
         <x:v>OESD</x:v>
       </x:c>
-      <x:c r="B14" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C14" s="69" t="str">
+      <x:c r="B15" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="C15" s="69" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="D14" s="41" t="str">
+      <x:c r="D15" s="41" t="str">
         <x:v>R/C</x:v>
       </x:c>
-      <x:c r="E14" s="63" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F14" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="G14" s="69" t="str">
+      <x:c r="E15" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F15" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G15" s="69" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="H14" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="I14" s="69" t="str">
+      <x:c r="H15" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="I15" s="69" t="str">
         <x:v>R/C</x:v>
       </x:c>
-      <x:c r="J14" s="41" t="str">
+      <x:c r="J15" s="41" t="str">
         <x:v>R/C</x:v>
       </x:c>
-      <x:c r="K14" s="69" t="str">
+      <x:c r="K15" s="69" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="L14" s="69" t="str">
+      <x:c r="L15" s="69" t="str">
         <x:v>R/C</x:v>
       </x:c>
-      <x:c r="M14" s="69" t="str">
+      <x:c r="M15" s="69" t="str">
         <x:v>R/C</x:v>
       </x:c>
-      <x:c r="N14" s="69" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="54" t="str">
-        <x:v>Gutshot</x:v>
-      </x:c>
-      <x:c r="B15" s="55" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C15" s="66" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="D15" s="55" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="E15" s="66" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="F15" s="56" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="G15" s="66" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="H15" s="56" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="I15" s="65" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="J15" s="56" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="K15" s="66" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="L15" s="84" t="str">
-        <x:v>R</x:v>
-      </x:c>
-      <x:c r="M15" s="66" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="N15" s="66" t="str">
+      <x:c r="N15" s="69" t="str">
         <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="54" t="str">
+        <x:v>Gutshot</x:v>
+      </x:c>
+      <x:c r="B16" s="55" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="C16" s="66" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="D16" s="55" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="E16" s="66" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="F16" s="56" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="G16" s="66" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="H16" s="56" t="str">
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="I16" s="65" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="J16" s="56" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="K16" s="66" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="L16" s="84" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="M16" s="66" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="N16" s="66" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="54" t="str">
         <x:v>2 overcards + BDFD</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="D16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="E16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="H16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="I16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="J16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="K16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="L16" s="66" t="str">
+      <x:c r="B17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="C17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="D17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="G17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="H17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L17" s="66" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="M16" s="66" t="str">
+      <x:c r="M17" s="66" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="N16" s="66" t="str">
+      <x:c r="N17" s="66" t="str">
         <x:v>C/F</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="37" t="str">
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="37" t="str">
         <x:v>Air</x:v>
       </x:c>
-      <x:c r="B17" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="D17" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="E17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="F17" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="G17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="H17" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="I17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="J17" s="41" t="str">
+      <x:c r="B18" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="C18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D18" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="E18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="F18" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="H18" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="J18" s="41" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="K17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="L17" s="69" t="str">
+      <x:c r="K18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="L18" s="69" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="M17" s="69" t="str">
+      <x:c r="M18" s="69" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="N17" s="69" t="str">
+      <x:c r="N18" s="69" t="str">
         <x:v>F/C</x:v>
       </x:c>
     </x:row>
@@ -3682,222 +3814,266 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
-      <x:c r="A13" s="54" t="str">
+      <x:c r="A13" s="37" t="str">
         <x:v>Weak pair</x:v>
       </x:c>
-      <x:c r="B13" s="80" t="str">
-        <x:v>F</x:v>
+      <x:c r="B13" s="49" t="str">
+        <x:v>C</x:v>
       </x:c>
       <x:c r="C13" s="82" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="D13" s="80" t="str">
+      <x:c r="D13" s="79" t="str">
         <x:v>F</x:v>
       </x:c>
       <x:c r="E13" s="82" t="str">
         <x:v>F</x:v>
       </x:c>
-      <x:c r="F13" s="56" t="str">
+      <x:c r="F13" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="H13" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="I13" s="69" t="str">
         <x:v>F/C</x:v>
       </x:c>
-      <x:c r="G13" s="65" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="H13" s="80" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="I13" s="82" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="J13" s="56" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="K13" s="82" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="L13" s="66" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="M13" s="82" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="N13" s="65" t="str">
+      <x:c r="J13" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="K13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="M13" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N13" s="64" t="str">
         <x:v>C</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
-      <x:c r="A14" s="37" t="str">
+      <x:c r="A14" s="54" t="str">
+        <x:v>Low pocket pair</x:v>
+      </x:c>
+      <x:c r="B14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="C14" s="83" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="E14" s="83" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="F14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G14" s="65" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="H14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I14" s="83" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="J14" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="K14" s="83" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="L14" s="83" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="M14" s="83" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="N14" s="66" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="37" t="str">
         <x:v>OESD</x:v>
       </x:c>
-      <x:c r="B14" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="C14" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="D14" s="41" t="str">
+      <x:c r="B15" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="C15" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="D15" s="41" t="str">
         <x:v>C/R</x:v>
       </x:c>
-      <x:c r="E14" s="63" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F14" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="G14" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="H14" s="41" t="str">
+      <x:c r="E15" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F15" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G15" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="H15" s="41" t="str">
         <x:v>C/F</x:v>
       </x:c>
-      <x:c r="I14" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="J14" s="75" t="str">
+      <x:c r="I15" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="J15" s="75" t="str">
         <x:v>R</x:v>
       </x:c>
-      <x:c r="K14" s="85" t="str">
+      <x:c r="K15" s="85" t="str">
         <x:v>R</x:v>
       </x:c>
-      <x:c r="L14" s="85" t="str">
+      <x:c r="L15" s="85" t="str">
         <x:v>R</x:v>
       </x:c>
-      <x:c r="M14" s="85" t="str">
+      <x:c r="M15" s="85" t="str">
         <x:v>R</x:v>
       </x:c>
-      <x:c r="N14" s="85" t="str">
+      <x:c r="N15" s="85" t="str">
         <x:v>R</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="24" customHeight="1">
-      <x:c r="A15" s="54" t="str">
-        <x:v>Gutshot</x:v>
-      </x:c>
-      <x:c r="B15" s="80" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C15" s="65" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="D15" s="55" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="E15" s="65" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="F15" s="55" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="G15" s="65" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="H15" s="80" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="I15" s="65" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="J15" s="56" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="K15" s="66" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="L15" s="84" t="str">
-        <x:v>R</x:v>
-      </x:c>
-      <x:c r="M15" s="66" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="N15" s="66" t="str">
-        <x:v>R/C</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="54" t="str">
+        <x:v>Gutshot</x:v>
+      </x:c>
+      <x:c r="B16" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="C16" s="65" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="D16" s="55" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="E16" s="65" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="F16" s="55" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G16" s="65" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="H16" s="80" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I16" s="65" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="J16" s="56" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="K16" s="66" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="L16" s="84" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="M16" s="66" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="N16" s="66" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="54" t="str">
         <x:v>2 overcards + BDFD</x:v>
       </x:c>
-      <x:c r="B16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="C16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="D16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="E16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="F16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="G16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="H16" s="59" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="I16" s="67" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="J16" s="55" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="K16" s="65" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="L16" s="65" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="M16" s="66" t="str">
+      <x:c r="B17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="C17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="D17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="E17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="F17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="G17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="H17" s="59" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="I17" s="67" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J17" s="55" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="K17" s="65" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="L17" s="65" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="M17" s="66" t="str">
         <x:v>C/F</x:v>
       </x:c>
-      <x:c r="N16" s="66" t="str">
+      <x:c r="N17" s="66" t="str">
         <x:v>F/C</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="24" customHeight="1">
-      <x:c r="A17" s="37" t="str">
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="37" t="str">
         <x:v>Air</x:v>
       </x:c>
-      <x:c r="B17" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="C17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="D17" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="E17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="F17" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="G17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="H17" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="I17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="J17" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="K17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="L17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="M17" s="83" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="N17" s="83" t="str">
+      <x:c r="B18" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="C18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D18" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="E18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="F18" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="G18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="H18" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="J18" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="K18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="L18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="M18" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="N18" s="82" t="str">
         <x:v>F</x:v>
       </x:c>
     </x:row>
@@ -4025,54 +4201,58 @@
         <x:v>Категории рук</x:v>
       </x:c>
       <x:c r="B12" s="87" t="str">
-        <x:v>7 made-категорий; затем OESD; Gutshot; 2 overcards + BDFD; Air</x:v>
+        <x:v>8 made-категорий; затем OESD; Gutshot; 2 overcards + BDFD; Air</x:v>
       </x:c>
       <x:c r="C12" s="3"/>
       <x:c r="D12" s="3"/>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="87" t="str">
-        <x:v>Приоритет неготовых</x:v>
+        <x:v>Карманные пары</x:v>
       </x:c>
       <x:c r="B13" s="87" t="str">
-        <x:v>OESD &gt; Gutshot &gt; 2 overcards + BDFD &gt; Air; BDFD без двух оверкарт уходит в Air</x:v>
+        <x:v>Underpair: между top и middle; Weak pair: между middle и low; Low pocket pair: ниже low</x:v>
       </x:c>
       <x:c r="C13" s="3"/>
       <x:c r="D13" s="3"/>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
       <x:c r="A14" s="87" t="str">
-        <x:v>Категории флопов</x:v>
+        <x:v>Приоритет неготовых</x:v>
       </x:c>
       <x:c r="B14" s="87" t="str">
-        <x:v>B13 — итоговые категории этой таблицы</x:v>
+        <x:v>OESD &gt; Gutshot &gt; 2 overcards + BDFD &gt; Air; BDFD без двух оверкарт уходит в Air</x:v>
       </x:c>
       <x:c r="C14" s="3"/>
       <x:c r="D14" s="3"/>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
       <x:c r="A15" s="87" t="str">
-        <x:v>Роль исходной B13</x:v>
+        <x:v>Категории флопов</x:v>
       </x:c>
       <x:c r="B15" s="87" t="str">
-        <x:v>Итоговые столбцы стратегии</x:v>
+        <x:v>B13 — итоговые категории этой таблицы</x:v>
       </x:c>
       <x:c r="C15" s="3"/>
       <x:c r="D15" s="3"/>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
       <x:c r="A16" s="87" t="str">
-        <x:v>JT9</x:v>
+        <x:v>Роль исходной B13</x:v>
       </x:c>
       <x:c r="B16" s="87" t="str">
-        <x:v>Исходная B13 = [J-8]x con; в 8-групповой таблице = Middle connected</x:v>
+        <x:v>Итоговые столбцы стратегии</x:v>
       </x:c>
       <x:c r="C16" s="3"/>
       <x:c r="D16" s="3"/>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
-      <x:c r="A17" s="3"/>
-      <x:c r="B17" s="3"/>
+      <x:c r="A17" s="87" t="str">
+        <x:v>JT9</x:v>
+      </x:c>
+      <x:c r="B17" s="87" t="str">
+        <x:v>Исходная B13 = [J-8]x con; в 8-групповой таблице = Middle connected</x:v>
+      </x:c>
       <x:c r="C17" s="3"/>
       <x:c r="D17" s="3"/>
     </x:row>
@@ -4083,144 +4263,136 @@
       <x:c r="D18" s="3"/>
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
-      <x:c r="A19" s="88" t="str">
+      <x:c r="A19" s="3"/>
+      <x:c r="B19" s="3"/>
+      <x:c r="C19" s="3"/>
+      <x:c r="D19" s="3"/>
+    </x:row>
+    <x:row r="20" ht="27" customHeight="1">
+      <x:c r="A20" s="88" t="str">
         <x:v>Категория флопов</x:v>
       </x:c>
-      <x:c r="B19" s="88" t="str">
+      <x:c r="B20" s="88" t="str">
         <x:v>Входящие B13 / определение</x:v>
       </x:c>
-      <x:c r="C19" s="88" t="str">
+      <x:c r="C20" s="88" t="str">
         <x:v>Количество</x:v>
       </x:c>
-      <x:c r="D19" s="88" t="str">
+      <x:c r="D20" s="88" t="str">
         <x:v>Пояснение</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="27" customHeight="1">
-      <x:c r="A20" s="91" t="str">
-        <x:v>ABB</x:v>
-      </x:c>
-      <x:c r="B20" s="91" t="str">
-        <x:v>A + две broadway-карты</x:v>
-      </x:c>
-      <x:c r="C20" s="92" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D20" s="91" t="str">
-        <x:v>B = T/J/Q/K; A отдельно</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
       <x:c r="A21" s="91" t="str">
-        <x:v>A[K/Q]x</x:v>
+        <x:v>ABB</x:v>
       </x:c>
       <x:c r="B21" s="91" t="str">
-        <x:v>A + K/Q + карта 9 и ниже</x:v>
+        <x:v>A + две broadway-карты</x:v>
       </x:c>
       <x:c r="C21" s="92" t="n">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D21" s="91" t="str">
-        <x:v>ABB исключён</x:v>
+        <x:v>B = T/J/Q/K; A отдельно</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
       <x:c r="A22" s="91" t="str">
-        <x:v>A[J-T][9-5]</x:v>
+        <x:v>A[K/Q]x</x:v>
       </x:c>
       <x:c r="B22" s="91" t="str">
-        <x:v>A + J/T + карта 9…5</x:v>
+        <x:v>A + K/Q + карта 9 и ниже</x:v>
       </x:c>
       <x:c r="C22" s="92" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D22" s="91" t="str"/>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D22" s="91" t="str">
+        <x:v>ABB исключён</x:v>
+      </x:c>
     </x:row>
     <x:row r="23" ht="27" customHeight="1">
       <x:c r="A23" s="91" t="str">
-        <x:v>A[J-T][4-2]</x:v>
+        <x:v>A[J-T][9-5]</x:v>
       </x:c>
       <x:c r="B23" s="91" t="str">
-        <x:v>A + J/T + карта 4…2</x:v>
+        <x:v>A + J/T + карта 9…5</x:v>
       </x:c>
       <x:c r="C23" s="92" t="n">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D23" s="91" t="str"/>
     </x:row>
     <x:row r="24" ht="27" customHeight="1">
       <x:c r="A24" s="91" t="str">
-        <x:v>A[9-7]x</x:v>
+        <x:v>A[J-T][4-2]</x:v>
       </x:c>
       <x:c r="B24" s="91" t="str">
-        <x:v>A + 9/8/7 + более низкая</x:v>
+        <x:v>A + J/T + карта 4…2</x:v>
       </x:c>
       <x:c r="C24" s="92" t="n">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D24" s="91" t="str"/>
     </x:row>
     <x:row r="25" ht="27" customHeight="1">
       <x:c r="A25" s="91" t="str">
-        <x:v>A[6-2]x</x:v>
+        <x:v>A[9-7]x</x:v>
       </x:c>
       <x:c r="B25" s="91" t="str">
-        <x:v>A + 6…3 + более низкая</x:v>
+        <x:v>A + 9/8/7 + более низкая</x:v>
       </x:c>
       <x:c r="C25" s="92" t="n">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D25" s="91" t="str"/>
     </x:row>
     <x:row r="26" ht="27" customHeight="1">
       <x:c r="A26" s="91" t="str">
-        <x:v>BBB</x:v>
+        <x:v>A[6-2]x</x:v>
       </x:c>
       <x:c r="B26" s="91" t="str">
-        <x:v>Без A; три broadway-карты</x:v>
+        <x:v>A + 6…3 + более низкая</x:v>
       </x:c>
       <x:c r="C26" s="92" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D26" s="91" t="str"/>
     </x:row>
     <x:row r="27" ht="27" customHeight="1">
       <x:c r="A27" s="91" t="str">
-        <x:v>BBx</x:v>
+        <x:v>BBB</x:v>
       </x:c>
       <x:c r="B27" s="91" t="str">
-        <x:v>Без A; две broadway + карта ≤9</x:v>
+        <x:v>Без A; три broadway-карты</x:v>
       </x:c>
       <x:c r="C27" s="92" t="n">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D27" s="91" t="str">
-        <x:v>JT9 исключён</x:v>
-      </x:c>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D27" s="91" t="str"/>
     </x:row>
     <x:row r="28" ht="27" customHeight="1">
       <x:c r="A28" s="91" t="str">
-        <x:v>K/Qx dis</x:v>
+        <x:v>BBx</x:v>
       </x:c>
       <x:c r="B28" s="91" t="str">
-        <x:v>Старшая K/Q; lower gap &gt;1</x:v>
+        <x:v>Без A; две broadway + карта ≤9</x:v>
       </x:c>
       <x:c r="C28" s="92" t="n">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D28" s="91" t="str">
-        <x:v>Не BBx</x:v>
+        <x:v>JT9 исключён</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="27" customHeight="1">
       <x:c r="A29" s="91" t="str">
-        <x:v>K/Qx con</x:v>
+        <x:v>K/Qx dis</x:v>
       </x:c>
       <x:c r="B29" s="91" t="str">
-        <x:v>Старшая K/Q; lower gap =1</x:v>
+        <x:v>Старшая K/Q; lower gap &gt;1</x:v>
       </x:c>
       <x:c r="C29" s="92" t="n">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D29" s="91" t="str">
         <x:v>Не BBx</x:v>
@@ -4228,47 +4400,55 @@
     </x:row>
     <x:row r="30" ht="27" customHeight="1">
       <x:c r="A30" s="91" t="str">
-        <x:v>[J-8]x dis</x:v>
+        <x:v>K/Qx con</x:v>
       </x:c>
       <x:c r="B30" s="91" t="str">
-        <x:v>Старшая J/T/9/8; lower gap &gt;1</x:v>
+        <x:v>Старшая K/Q; lower gap =1</x:v>
       </x:c>
       <x:c r="C30" s="92" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D30" s="91" t="str"/>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D30" s="91" t="str">
+        <x:v>Не BBx</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" ht="27" customHeight="1">
       <x:c r="A31" s="91" t="str">
-        <x:v>[J-8]x con</x:v>
+        <x:v>[J-8]x dis</x:v>
       </x:c>
       <x:c r="B31" s="91" t="str">
-        <x:v>Старшая J/T/9/8; lower gap =1</x:v>
+        <x:v>Старшая J/T/9/8; lower gap &gt;1</x:v>
       </x:c>
       <x:c r="C31" s="92" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D31" s="91" t="str">
-        <x:v>Включает JT9</x:v>
-      </x:c>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D31" s="91" t="str"/>
     </x:row>
     <x:row r="32" ht="27" customHeight="1">
       <x:c r="A32" s="91" t="str">
+        <x:v>[J-8]x con</x:v>
+      </x:c>
+      <x:c r="B32" s="91" t="str">
+        <x:v>Старшая J/T/9/8; lower gap =1</x:v>
+      </x:c>
+      <x:c r="C32" s="92" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D32" s="91" t="str">
+        <x:v>Включает JT9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="27" customHeight="1">
+      <x:c r="A33" s="91" t="str">
         <x:v>[7-4]x</x:v>
       </x:c>
-      <x:c r="B32" s="91" t="str">
+      <x:c r="B33" s="91" t="str">
         <x:v>Старшая карта 7 или ниже</x:v>
       </x:c>
-      <x:c r="C32" s="92" t="n">
+      <x:c r="C33" s="92" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D32" s="91" t="str"/>
-    </x:row>
-    <x:row r="33" ht="27" customHeight="1">
-      <x:c r="A33" s="3"/>
-      <x:c r="B33" s="3"/>
-      <x:c r="C33" s="3"/>
-      <x:c r="D33" s="3"/>
+      <x:c r="D33" s="91" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_simplified_flop_strategy.xlsx
+++ b/datasets/STU004__RNG002_UTG-vs-BTN__BRD001_FLOP4/analysis/STU004_simplified_flop_strategy.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd9c6ab5b75a54ee3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="R3ecb4b5b6bb9470c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="Rba2303a3c7754707"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R097ad820e8be473c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="Ra6d00eb73eb34121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="R822310e1cd6241da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rbd71ce5686af429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01 UTG cbet" sheetId="2" r:id="R0f0b5ce340db41cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02 BTN stab" sheetId="3" r:id="Rf89444da4ee44571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 BTN vs cbet" sheetId="4" r:id="R2c3aaf9bfae84e95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 UTG vs stab" sheetId="5" r:id="Rbcd047e42388442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="6" r:id="R15cab2a34a394f4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1638,43 +1638,43 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="37" t="str">
-        <x:v>Third pair</x:v>
+        <x:v>Weak pair</x:v>
       </x:c>
       <x:c r="B12" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="C12" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D12" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E12" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="F12" s="45" t="str">
-        <x:v>B</x:v>
+      <x:c r="C12" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D12" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E12" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F12" s="49" t="str">
+        <x:v>X</x:v>
       </x:c>
       <x:c r="G12" s="62" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H12" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I12" s="69" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="J12" s="41" t="str">
+      <x:c r="H12" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="K12" s="64" t="str">
-        <x:v>X</x:v>
+      <x:c r="I12" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J12" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="K12" s="63" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L12" s="64" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="M12" s="64" t="str">
-        <x:v>X</x:v>
+      <x:c r="M12" s="63" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="N12" s="64" t="str">
         <x:v>X</x:v>
@@ -1682,43 +1682,43 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="37" t="str">
-        <x:v>Weak pair</x:v>
+        <x:v>Third pair</x:v>
       </x:c>
       <x:c r="B13" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="C13" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D13" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="E13" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F13" s="49" t="str">
-        <x:v>X</x:v>
+      <x:c r="C13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D13" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F13" s="45" t="str">
+        <x:v>B</x:v>
       </x:c>
       <x:c r="G13" s="62" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="H13" s="41" t="str">
+      <x:c r="H13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I13" s="69" t="str">
+        <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="J13" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="I13" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="J13" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="K13" s="63" t="str">
-        <x:v>—</x:v>
+      <x:c r="K13" s="64" t="str">
+        <x:v>X</x:v>
       </x:c>
       <x:c r="L13" s="64" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="M13" s="63" t="str">
-        <x:v>—</x:v>
+      <x:c r="M13" s="64" t="str">
+        <x:v>X</x:v>
       </x:c>
       <x:c r="N13" s="64" t="str">
         <x:v>X</x:v>
@@ -2349,90 +2349,90 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="37" t="str">
-        <x:v>Third pair</x:v>
+        <x:v>Weak pair</x:v>
       </x:c>
       <x:c r="B12" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="C12" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="D12" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="E12" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="F12" s="45" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="G12" s="62" t="str">
-        <x:v>B</x:v>
+      <x:c r="C12" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="D12" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="E12" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="F12" s="41" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="G12" s="69" t="str">
+        <x:v>B/X</x:v>
       </x:c>
       <x:c r="H12" s="49" t="str">
         <x:v>X</x:v>
       </x:c>
-      <x:c r="I12" s="62" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="J12" s="41" t="str">
+      <x:c r="I12" s="64" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="J12" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="K12" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L12" s="69" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="K12" s="69" t="str">
-        <x:v>X/B</x:v>
-      </x:c>
-      <x:c r="L12" s="69" t="str">
+      <x:c r="M12" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="N12" s="69" t="str">
         <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="M12" s="69" t="str">
-        <x:v>B/X</x:v>
-      </x:c>
-      <x:c r="N12" s="62" t="str">
-        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="37" t="str">
-        <x:v>Weak pair</x:v>
+        <x:v>Third pair</x:v>
       </x:c>
       <x:c r="B13" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="C13" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="D13" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="E13" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="F13" s="41" t="str">
+      <x:c r="C13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="D13" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="E13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="F13" s="45" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="G13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="H13" s="49" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="I13" s="62" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="J13" s="41" t="str">
         <x:v>X/B</x:v>
       </x:c>
-      <x:c r="G13" s="69" t="str">
+      <x:c r="K13" s="69" t="str">
+        <x:v>X/B</x:v>
+      </x:c>
+      <x:c r="L13" s="69" t="str">
         <x:v>B/X</x:v>
       </x:c>
-      <x:c r="H13" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="I13" s="64" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="J13" s="49" t="str">
-        <x:v>X</x:v>
-      </x:c>
-      <x:c r="K13" s="63" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="L13" s="69" t="str">
-        <x:v>X/B</x:v>
-      </x:c>
-      <x:c r="M13" s="63" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="N13" s="69" t="str">
+      <x:c r="M13" s="69" t="str">
         <x:v>B/X</x:v>
+      </x:c>
+      <x:c r="N13" s="62" t="str">
+        <x:v>B</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
@@ -3060,22 +3060,22 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="37" t="str">
-        <x:v>Third pair</x:v>
+        <x:v>Weak pair</x:v>
       </x:c>
       <x:c r="B12" s="49" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="C12" s="69" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="D12" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="E12" s="69" t="str">
-        <x:v>R/C</x:v>
-      </x:c>
-      <x:c r="F12" s="49" t="str">
-        <x:v>C</x:v>
+      <x:c r="C12" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D12" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="E12" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="F12" s="41" t="str">
+        <x:v>F/C</x:v>
       </x:c>
       <x:c r="G12" s="64" t="str">
         <x:v>C</x:v>
@@ -3084,19 +3084,19 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="I12" s="69" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="J12" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="K12" s="69" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="L12" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="M12" s="69" t="str">
-        <x:v>C/R</x:v>
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="J12" s="41" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+      <x:c r="K12" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L12" s="69" t="str">
+        <x:v>C/F</x:v>
+      </x:c>
+      <x:c r="M12" s="63" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="N12" s="64" t="str">
         <x:v>C</x:v>
@@ -3104,22 +3104,22 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="37" t="str">
-        <x:v>Weak pair</x:v>
+        <x:v>Third pair</x:v>
       </x:c>
       <x:c r="B13" s="49" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="C13" s="82" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="D13" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="E13" s="82" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="F13" s="41" t="str">
-        <x:v>F/C</x:v>
+      <x:c r="C13" s="69" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="D13" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="E13" s="69" t="str">
+        <x:v>R/C</x:v>
+      </x:c>
+      <x:c r="F13" s="49" t="str">
+        <x:v>C</x:v>
       </x:c>
       <x:c r="G13" s="64" t="str">
         <x:v>C</x:v>
@@ -3128,19 +3128,19 @@
         <x:v>C</x:v>
       </x:c>
       <x:c r="I13" s="69" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="J13" s="41" t="str">
-        <x:v>C/F</x:v>
-      </x:c>
-      <x:c r="K13" s="63" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="L13" s="69" t="str">
-        <x:v>C/F</x:v>
-      </x:c>
-      <x:c r="M13" s="63" t="str">
-        <x:v>—</x:v>
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="J13" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="K13" s="69" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="L13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="M13" s="69" t="str">
+        <x:v>C/R</x:v>
       </x:c>
       <x:c r="N13" s="64" t="str">
         <x:v>C</x:v>
@@ -3771,43 +3771,43 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="37" t="str">
-        <x:v>Third pair</x:v>
+        <x:v>Weak pair</x:v>
       </x:c>
       <x:c r="B12" s="49" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="C12" s="85" t="str">
-        <x:v>R</x:v>
-      </x:c>
-      <x:c r="D12" s="41" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="E12" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="F12" s="41" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="G12" s="85" t="str">
-        <x:v>R</x:v>
+      <x:c r="C12" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="D12" s="79" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="E12" s="82" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="F12" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="G12" s="64" t="str">
+        <x:v>C</x:v>
       </x:c>
       <x:c r="H12" s="49" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I12" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="J12" s="41" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="K12" s="69" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="L12" s="69" t="str">
-        <x:v>C/R</x:v>
-      </x:c>
-      <x:c r="M12" s="64" t="str">
-        <x:v>C</x:v>
+      <x:c r="I12" s="69" t="str">
+        <x:v>F/C</x:v>
+      </x:c>
+      <x:c r="J12" s="49" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="K12" s="63" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L12" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="M12" s="63" t="str">
+        <x:v>—</x:v>
       </x:c>
       <x:c r="N12" s="64" t="str">
         <x:v>C</x:v>
@@ -3815,43 +3815,43 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="37" t="str">
-        <x:v>Weak pair</x:v>
+        <x:v>Third pair</x:v>
       </x:c>
       <x:c r="B13" s="49" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="C13" s="82" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="D13" s="79" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="E13" s="82" t="str">
-        <x:v>F</x:v>
-      </x:c>
-      <x:c r="F13" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="G13" s="64" t="str">
-        <x:v>C</x:v>
+      <x:c r="C13" s="85" t="str">
+        <x:v>R</x:v>
+      </x:c>
+      <x:c r="D13" s="41" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="E13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="F13" s="41" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="G13" s="85" t="str">
+        <x:v>R</x:v>
       </x:c>
       <x:c r="H13" s="49" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="I13" s="69" t="str">
-        <x:v>F/C</x:v>
-      </x:c>
-      <x:c r="J13" s="49" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="K13" s="63" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="L13" s="64" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="M13" s="63" t="str">
-        <x:v>—</x:v>
+      <x:c r="I13" s="64" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="J13" s="41" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="K13" s="69" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="L13" s="69" t="str">
+        <x:v>C/R</x:v>
+      </x:c>
+      <x:c r="M13" s="64" t="str">
+        <x:v>C</x:v>
       </x:c>
       <x:c r="N13" s="64" t="str">
         <x:v>C</x:v>
